--- a/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/TN WP 2026-27/SL 2.0/Kallakuruchi.xlsx
+++ b/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/TN WP 2026-27/SL 2.0/Kallakuruchi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Grv\Grv\05 GIT\01_masterRepo\06_Office_Related\01_NSO_work\06_SL_to_PIVOT_to_Compare_with_WP\TN WP 2026-27\SL 2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75A71E1-0CC6-4D29-8C2B-E3E101879624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B7D8ED0-0DEA-4619-B001-0ED67C0665CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,12 +23,23 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Working sheet'!$A$1:$L$18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Working sheet'!$5:$6</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="158">
   <si>
     <t>State Sample</t>
   </si>
@@ -481,9 +492,6 @@
     <t>Thiyagai</t>
   </si>
   <si>
-    <t>TOTAL = 40</t>
-  </si>
-  <si>
     <t># Group B Village</t>
   </si>
   <si>
@@ -505,7 +513,10 @@
     <t xml:space="preserve">6                        3                       </t>
   </si>
   <si>
-    <t>Bajra - K</t>
+    <t>TOTAL = 38</t>
+  </si>
+  <si>
+    <t>Bajra (K)</t>
   </si>
 </sst>
 </file>
@@ -862,9 +873,6 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -879,6 +887,30 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -901,30 +933,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -932,6 +940,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1256,104 +1267,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
     </row>
     <row r="2" spans="1:12" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
     </row>
     <row r="3" spans="1:12" s="6" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="58" t="s">
+      <c r="A3" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="57" t="s">
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
+      <c r="L3" s="64"/>
     </row>
     <row r="4" spans="1:12" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="61" t="s">
+      <c r="A4" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="57" t="s">
-        <v>152</v>
-      </c>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="64" t="s">
+        <v>151</v>
+      </c>
+      <c r="K4" s="64"/>
+      <c r="L4" s="64"/>
     </row>
     <row r="5" spans="1:12" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="69" t="s">
+      <c r="B5" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="66" t="s">
+      <c r="C5" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="67"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="64" t="s">
+      <c r="D5" s="60"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64" t="s">
+      <c r="G5" s="57"/>
+      <c r="H5" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="64"/>
-      <c r="J5" s="64" t="s">
+      <c r="I5" s="57"/>
+      <c r="J5" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="K5" s="64"/>
-      <c r="L5" s="64" t="s">
+      <c r="K5" s="57"/>
+      <c r="L5" s="57" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="65"/>
-      <c r="B6" s="70"/>
+      <c r="A6" s="58"/>
+      <c r="B6" s="63"/>
       <c r="C6" s="7" t="s">
         <v>7</v>
       </c>
@@ -1381,7 +1392,7 @@
       <c r="K6" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="L6" s="64"/>
+      <c r="L6" s="57"/>
     </row>
     <row r="7" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
@@ -1488,10 +1499,10 @@
         <v>4</v>
       </c>
       <c r="J9" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="K9" s="5" t="s">
         <v>153</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>154</v>
       </c>
       <c r="L9" s="5">
         <v>21</v>
@@ -1716,7 +1727,7 @@
         <v>2</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K15" s="5" t="s">
         <v>85</v>
@@ -1817,6 +1828,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="J4:L4"/>
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="F5:G5"/>
@@ -1824,12 +1841,6 @@
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="J4:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
@@ -3362,140 +3373,140 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="56"/>
+      <c r="U2" s="56"/>
+      <c r="V2" s="56"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="52"/>
+      <c r="B3" s="51"/>
       <c r="C3" s="37"/>
       <c r="D3" s="37"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="51" t="s">
+      <c r="G3" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="56"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
-      <c r="Q3" s="51" t="s">
+      <c r="Q3" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="R3" s="51"/>
-      <c r="S3" s="51"/>
-      <c r="T3" s="51"/>
-      <c r="U3" s="51"/>
-      <c r="V3" s="51"/>
+      <c r="R3" s="56"/>
+      <c r="S3" s="56"/>
+      <c r="T3" s="56"/>
+      <c r="U3" s="56"/>
+      <c r="V3" s="56"/>
     </row>
     <row r="4" spans="1:22" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53" t="s">
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53" t="s">
+      <c r="G4" s="52"/>
+      <c r="H4" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53" t="s">
+      <c r="I4" s="52"/>
+      <c r="J4" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="K4" s="53"/>
-      <c r="L4" s="54" t="s">
+      <c r="K4" s="52"/>
+      <c r="L4" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54" t="s">
+      <c r="M4" s="53"/>
+      <c r="N4" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="O4" s="54"/>
-      <c r="P4" s="55" t="s">
+      <c r="O4" s="53"/>
+      <c r="P4" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="Q4" s="56"/>
+      <c r="Q4" s="55"/>
       <c r="R4" s="42" t="s">
         <v>54</v>
       </c>
       <c r="S4" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="T4" s="54" t="s">
+      <c r="T4" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="U4" s="54"/>
-      <c r="V4" s="54" t="s">
+      <c r="U4" s="53"/>
+      <c r="V4" s="53" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A5" s="54"/>
-      <c r="B5" s="54"/>
+      <c r="A5" s="53"/>
+      <c r="B5" s="53"/>
       <c r="C5" s="11" t="s">
         <v>20</v>
       </c>
@@ -3553,11 +3564,11 @@
       <c r="U5" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="V5" s="54"/>
+      <c r="V5" s="53"/>
     </row>
     <row r="6" spans="1:22" s="13" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="54"/>
-      <c r="B6" s="54"/>
+      <c r="A6" s="53"/>
+      <c r="B6" s="53"/>
       <c r="C6" s="12" t="s">
         <v>25</v>
       </c>
@@ -3618,30 +3629,30 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="53"/>
-      <c r="N7" s="53"/>
-      <c r="O7" s="53"/>
-      <c r="P7" s="53"/>
-      <c r="Q7" s="53"/>
-      <c r="R7" s="53"/>
-      <c r="S7" s="53"/>
-      <c r="T7" s="53"/>
-      <c r="U7" s="53"/>
-      <c r="V7" s="53"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="52"/>
+      <c r="K7" s="52"/>
+      <c r="L7" s="52"/>
+      <c r="M7" s="52"/>
+      <c r="N7" s="52"/>
+      <c r="O7" s="52"/>
+      <c r="P7" s="52"/>
+      <c r="Q7" s="52"/>
+      <c r="R7" s="52"/>
+      <c r="S7" s="52"/>
+      <c r="T7" s="52"/>
+      <c r="U7" s="52"/>
+      <c r="V7" s="52"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="23" t="s">
@@ -3730,30 +3741,30 @@
       <c r="V10" s="11"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="53" t="s">
+      <c r="A11" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="53"/>
-      <c r="K11" s="53"/>
-      <c r="L11" s="53"/>
-      <c r="M11" s="53"/>
-      <c r="N11" s="53"/>
-      <c r="O11" s="53"/>
-      <c r="P11" s="53"/>
-      <c r="Q11" s="53"/>
-      <c r="R11" s="53"/>
-      <c r="S11" s="53"/>
-      <c r="T11" s="53"/>
-      <c r="U11" s="53"/>
-      <c r="V11" s="53"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="52"/>
+      <c r="K11" s="52"/>
+      <c r="L11" s="52"/>
+      <c r="M11" s="52"/>
+      <c r="N11" s="52"/>
+      <c r="O11" s="52"/>
+      <c r="P11" s="52"/>
+      <c r="Q11" s="52"/>
+      <c r="R11" s="52"/>
+      <c r="S11" s="52"/>
+      <c r="T11" s="52"/>
+      <c r="U11" s="52"/>
+      <c r="V11" s="52"/>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="23" t="s">
@@ -4550,7 +4561,7 @@
         <v>113</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C38" s="17"/>
       <c r="D38" s="17"/>
@@ -4672,11 +4683,16 @@
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="G3:M3"/>
+    <mergeCell ref="Q3:V3"/>
+    <mergeCell ref="A3:B3"/>
     <mergeCell ref="A7:V7"/>
     <mergeCell ref="A11:V11"/>
     <mergeCell ref="J4:K4"/>
@@ -4690,11 +4706,6 @@
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:I4"/>
-    <mergeCell ref="A1:V1"/>
-    <mergeCell ref="A2:V2"/>
-    <mergeCell ref="G3:M3"/>
-    <mergeCell ref="Q3:V3"/>
-    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J9" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
@@ -6235,134 +6246,134 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="56"/>
+      <c r="U2" s="56"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="74" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="51" t="s">
+      <c r="G3" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="56"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
-      <c r="Q3" s="51" t="s">
+      <c r="Q3" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="R3" s="51"/>
-      <c r="S3" s="51"/>
-      <c r="T3" s="51"/>
-      <c r="U3" s="51"/>
+      <c r="R3" s="56"/>
+      <c r="S3" s="56"/>
+      <c r="T3" s="56"/>
+      <c r="U3" s="56"/>
     </row>
     <row r="4" spans="1:21" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53" t="s">
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52" t="s">
         <v>138</v>
       </c>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53" t="s">
+      <c r="G4" s="52"/>
+      <c r="H4" s="52" t="s">
         <v>157</v>
       </c>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53" t="s">
+      <c r="I4" s="52"/>
+      <c r="J4" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="K4" s="53"/>
-      <c r="L4" s="54" t="s">
+      <c r="K4" s="52"/>
+      <c r="L4" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54" t="s">
+      <c r="M4" s="53"/>
+      <c r="N4" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="O4" s="54"/>
-      <c r="P4" s="55" t="s">
+      <c r="O4" s="53"/>
+      <c r="P4" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="Q4" s="56"/>
+      <c r="Q4" s="55"/>
       <c r="R4" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="S4" s="54" t="s">
+      <c r="S4" s="53" t="s">
         <v>136</v>
       </c>
-      <c r="T4" s="54"/>
-      <c r="U4" s="54" t="s">
+      <c r="T4" s="53"/>
+      <c r="U4" s="53" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A5" s="54"/>
-      <c r="B5" s="54"/>
+      <c r="A5" s="53"/>
+      <c r="B5" s="53"/>
       <c r="C5" s="11" t="s">
         <v>20</v>
       </c>
@@ -6417,11 +6428,11 @@
       <c r="T5" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="U5" s="54"/>
+      <c r="U5" s="53"/>
     </row>
     <row r="6" spans="1:21" s="13" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="54"/>
-      <c r="B6" s="54"/>
+      <c r="A6" s="53"/>
+      <c r="B6" s="53"/>
       <c r="C6" s="12" t="s">
         <v>25</v>
       </c>
@@ -6481,29 +6492,29 @@
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="72" t="s">
+      <c r="A7" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="73"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="73"/>
-      <c r="H7" s="73"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="73"/>
-      <c r="K7" s="73"/>
-      <c r="L7" s="73"/>
-      <c r="M7" s="73"/>
-      <c r="N7" s="73"/>
-      <c r="O7" s="73"/>
-      <c r="P7" s="73"/>
-      <c r="Q7" s="73"/>
-      <c r="R7" s="73"/>
-      <c r="S7" s="73"/>
-      <c r="T7" s="73"/>
-      <c r="U7" s="73"/>
+      <c r="B7" s="72"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="72"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="72"/>
+      <c r="K7" s="72"/>
+      <c r="L7" s="72"/>
+      <c r="M7" s="72"/>
+      <c r="N7" s="72"/>
+      <c r="O7" s="72"/>
+      <c r="P7" s="72"/>
+      <c r="Q7" s="72"/>
+      <c r="R7" s="72"/>
+      <c r="S7" s="72"/>
+      <c r="T7" s="72"/>
+      <c r="U7" s="72"/>
     </row>
     <row r="8" spans="1:21" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
@@ -6651,29 +6662,29 @@
       <c r="U12" s="11"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="53"/>
-      <c r="K13" s="53"/>
-      <c r="L13" s="53"/>
-      <c r="M13" s="53"/>
-      <c r="N13" s="53"/>
-      <c r="O13" s="53"/>
-      <c r="P13" s="53"/>
-      <c r="Q13" s="53"/>
-      <c r="R13" s="53"/>
-      <c r="S13" s="53"/>
-      <c r="T13" s="53"/>
-      <c r="U13" s="53"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="52"/>
+      <c r="K13" s="52"/>
+      <c r="L13" s="52"/>
+      <c r="M13" s="52"/>
+      <c r="N13" s="52"/>
+      <c r="O13" s="52"/>
+      <c r="P13" s="52"/>
+      <c r="Q13" s="52"/>
+      <c r="R13" s="52"/>
+      <c r="S13" s="52"/>
+      <c r="T13" s="52"/>
+      <c r="U13" s="52"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="23" t="s">
@@ -7018,9 +7029,7 @@
       <c r="Q25" s="17"/>
       <c r="R25" s="17"/>
       <c r="S25" s="17"/>
-      <c r="T25" s="30" t="s">
-        <v>56</v>
-      </c>
+      <c r="T25" s="30"/>
       <c r="U25" s="17"/>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -7076,27 +7085,27 @@
       <c r="U27" s="49"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A28" s="74"/>
-      <c r="B28" s="74"/>
-      <c r="C28" s="74"/>
-      <c r="D28" s="74"/>
-      <c r="E28" s="74"/>
-      <c r="F28" s="74"/>
-      <c r="G28" s="74"/>
-      <c r="H28" s="74"/>
-      <c r="I28" s="74"/>
-      <c r="J28" s="74"/>
-      <c r="K28" s="74"/>
-      <c r="L28" s="74"/>
-      <c r="M28" s="74"/>
-      <c r="N28" s="74"/>
-      <c r="O28" s="74"/>
-      <c r="P28" s="74"/>
-      <c r="Q28" s="74"/>
-      <c r="R28" s="74"/>
-      <c r="S28" s="74"/>
-      <c r="T28" s="74"/>
-      <c r="U28" s="74"/>
+      <c r="A28" s="73"/>
+      <c r="B28" s="73"/>
+      <c r="C28" s="73"/>
+      <c r="D28" s="73"/>
+      <c r="E28" s="73"/>
+      <c r="F28" s="73"/>
+      <c r="G28" s="73"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73"/>
+      <c r="J28" s="73"/>
+      <c r="K28" s="73"/>
+      <c r="L28" s="73"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="73"/>
+      <c r="O28" s="73"/>
+      <c r="P28" s="73"/>
+      <c r="Q28" s="73"/>
+      <c r="R28" s="73"/>
+      <c r="S28" s="73"/>
+      <c r="T28" s="73"/>
+      <c r="U28" s="73"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="33" t="s">
@@ -7117,18 +7126,23 @@
       <c r="N29" s="33"/>
       <c r="O29" s="33"/>
       <c r="P29" s="33" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q29" s="36"/>
       <c r="R29" s="33"/>
-      <c r="S29" s="51" t="s">
-        <v>149</v>
-      </c>
-      <c r="T29" s="51"/>
+      <c r="S29" s="56" t="s">
+        <v>156</v>
+      </c>
+      <c r="T29" s="56"/>
       <c r="U29" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="G3:M3"/>
+    <mergeCell ref="Q3:U3"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="F4:G4"/>
@@ -7144,11 +7158,6 @@
     <mergeCell ref="S4:T4"/>
     <mergeCell ref="U4:U5"/>
     <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:U2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="G3:M3"/>
-    <mergeCell ref="Q3:U3"/>
   </mergeCells>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape" r:id="rId1"/>
